--- a/asignaturas/fisica/propuesta/Propuesta_Fisica_G05-G08.xlsx
+++ b/asignaturas/fisica/propuesta/Propuesta_Fisica_G05-G08.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -577,12 +577,12 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>CO 2, SG 3, UY 5 (Imanes y polos magnéticos); prerrequisito: Imanes y polos magnéticos (6.°) de Campo magnético y magnetismo terrestre (5.°), confianza alta</t>
+          <t>AU 3, CO 2, ENG 2, SG 3, UY 5 (Imanes y polos magnéticos); prerrequisito: Imanes y polos magnéticos (6.°) de Campo magnético y magnetismo terrestre (5.°), confianza alta</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>Hoy el campo magnético terrestre (5.9) se estudia un año antes que los imanes. Los tres países enseñan los imanes entre 2.° y 5.°. El tema pasa a 5.°, justo antes de 5.9.</t>
+          <t>Hoy el campo magnético terrestre (5.9) se estudia un año antes que los imanes. Los cinco países, incluidos Inglaterra, Australia y Singapur, enseñan los imanes entre 2.° y 5.°. El tema pasa a 5.°, antes de 5.9.</t>
         </is>
       </c>
     </row>
@@ -625,12 +625,12 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>CO 4, SG 5 (Conductores y aislantes eléctricos); prerrequisito: Conductores y aislantes eléctricos (hoy en 11.°, G11-FIS-U6-6.3) de Circuito eléctrico simple (6.°), confianza alta</t>
+          <t>AU 5, CO 4.5, ENG 2, SG 5 (Conductores y aislantes eléctricos); prerrequisito: Conductores y aislantes eléctricos (hoy en 11.°, G11-FIS-U6-6.3) de Circuito eléctrico simple (6.°), confianza alta</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>Hoy llega en 11.°, cinco grados después de los circuitos de 6.°. Colombia y Singapur lo enseñan en 4.° y 5.°. Se paga con la fusión 3.</t>
+          <t>Hoy llega en 11.°, cinco grados después de los circuitos de 6.°. Inglaterra, Australia, Singapur y Colombia lo enseñan entre 2.° y 5.°. Se paga con la fusión 3.</t>
         </is>
       </c>
     </row>
@@ -727,12 +727,12 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>CO 4, UY 5 (Ley de gravitación universal); hoy solo en 10.° (G10-FIS-U5-5.7)</t>
+          <t>CO 4.5, ENG 6, UY 5 (Ley de gravitación universal); hoy solo en 10.° (G10-FIS-U5-5.7)</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>Colombia y Uruguay introducen la gravitación en 4.° y 5.°; El Salvador, en 10.°. Se trata de forma cualitativa; el cálculo con la ley de gravitación sigue en 10.°. Se paga con la fusión 5.</t>
+          <t>Colombia y Uruguay introducen la gravitación en 4.° y 5.° e Inglaterra en 6.°; El Salvador, en 10.°. Se trata de forma cualitativa; el cálculo sigue en 10.°. Se paga con la fusión 5.</t>
         </is>
       </c>
     </row>
@@ -796,51 +796,45 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>dividir</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>G06-CIE-U1-1.2</t>
-        </is>
-      </c>
+          <t>nuevo</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="n"/>
       <c r="F7" s="3" t="n">
         <v>5</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2. Mecánica. (5.°, después de 2.16); la parte del empuje queda en 1. Fluidos. (6.°, después de 1.3)</t>
+          <t>10. Electricidad y luz</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>2.17. Experimentación con la flotación y el hundimiento de objetos en el agua. | 1.2. Explicación del empuje mediante el principio de Arquímedes (se mantiene en 6.°, después de 1.3).</t>
+          <t>10.2. Experimentación con la reflexión de la luz y la formación de imágenes en espejos planos.</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Predice si distintos objetos flotan o se hunden, lo comprueba y explica el resultado comparando su material y su forma. | Mide con un dinamómetro la pérdida aparente de peso de un objeto sumergido y la relaciona con el volumen de agua desalojada.</t>
+          <t>Usa una linterna y un espejo plano para comprobar que el ángulo de incidencia es igual al de reflexión y describe la imagen que forma el espejo (tamaño, distancia, inversión lateral).</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>Flotación y hundimiento, Principio de Arquímedes: empuje</t>
+          <t>Reflexión de la luz, Espejos planos e imágenes</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>CO 4, SG 3, UY 4 (Flotación y hundimiento); prerrequisito: Presión hidrostática y atmosférica de Principio de Arquímedes: empuje, confianza alta</t>
+          <t>AU 4, CO 3, ENG 2, SG 4, UY 4 (Reflexión de la luz); T8_27-P3.1 Propiedades de la luz (reforzar: 0 temas en el ciclo); ENG 6, UY 4 (Espejos planos e imágenes; bloqueo Reflexión de la luz resuelto en el mismo tema)</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>El tema mezcla flotación (países: 3.° y 4.°) y empuje de Arquímedes, que necesita la presión (1.3). Se separan para adelantar lo primero y dejar el empuje después de la presión. Se paga con la fusión 7.</t>
+          <t>La luz no aparece en ningún tema de 5.° a 8.° y el objetivo TIMSS P3.1 queda sin cobertura. Los cinco países enseñan la reflexión entre 2.° y 4.°. Se paga con la fusión 7.</t>
         </is>
       </c>
     </row>
@@ -855,7 +849,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>G06-CIE-U1-1.7, G06-CIE-U1-1.8</t>
+          <t>G06-CIE-U1-1.4, G06-CIE-U1-1.5</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
@@ -869,32 +863,32 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1. Fluidos.</t>
+          <t>1. Fluidos. (coordinar con Química: 4.7 y 4.8 de 6.°, fuerzas intermoleculares)</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1.7. Indagación y aplicación del principio de Bernoulli.</t>
+          <t>1.4. Demostración experimental de la capilaridad y la tensión superficial y su explicación por la atracción entre partículas.</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Demuestra con experimentos sencillos (hoja de papel, atomizador) que la presión disminuye donde el fluido va más rápido y explica una aplicación cotidiana.</t>
+          <t>Observa el ascenso del agua en tubos o en papel y la flotación de un clip en el agua, y explica ambos fenómenos con la atracción entre partículas.</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Hidrodinámica: continuidad y Bernoulli</t>
+          <t>Tensión superficial y capilaridad, Fuerzas intermoleculares</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>fusión: ambos temas trabajan Hidrodinámica: continuidad y Bernoulli (1.6 también); prerrequisitos: Presión hidrostática y atmosférica; Conservación de la energía mecánica</t>
+          <t>fusión: ambos temas trabajan Tensión superficial y capilaridad</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Bernoulli ocupa tres temas en 6.° y depende de dos prerrequisitos que el archivo marca como tardíos. Unir indagación y aplicación reduce su peso y libera el tema de la acción 6.</t>
+          <t>Vinculación y demostración de la capilaridad son el mismo contenido. El tema unido explica el fenómeno por la atracción entre partículas, que Química trabaja en 4.7 y 4.8 de 6.°. Libera el tema de la acción 6.</t>
         </is>
       </c>
     </row>
@@ -913,36 +907,36 @@
       </c>
       <c r="E9" s="3" t="n"/>
       <c r="F9" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>10. Electricidad y luz</t>
+          <t>3. Electricidad y magnetismo. (antes de 3.1)</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>10.2. Experimentación con la reflexión de la luz en espejos y superficies.</t>
+          <t>3.10. Demostración experimental de la electrización de los cuerpos por frotamiento, contacto e inducción.</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Usa una linterna y un espejo plano para comprobar que el ángulo de incidencia es igual al de reflexión y explica cómo vemos los objetos que no emiten luz.</t>
+          <t>Electriza objetos por frotamiento, contacto e inducción, observa atracción y repulsión y lo explica con el paso de electrones entre los cuerpos.</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>Reflexión de la luz</t>
+          <t>Carga eléctrica y electrización</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>CO 3, SG 4, UY 4 (Reflexión de la luz); T8_27-P3.1 Propiedades de la luz (reforzar: 0 temas en el ciclo)</t>
+          <t>CO 6, ENG 6, UY 5 (Carga eléctrica y electrización); prerrequisito: Carga eléctrica y electrización (hoy en 9.°, G09-CIE-U6-6.1) de Corriente, voltaje y resistencia (6.°), confianza alta</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>La luz no aparece en ningún tema de 5.° a 8.°, y el objetivo TIMSS P3.1 queda sin cobertura. Los tres países enseñan la reflexión entre 3.° y 4.°. Se paga con la fusión 9.</t>
+          <t>En 6.° se mide la corriente sin haber visto la carga eléctrica, que llega en 9.°. Inglaterra y Colombia la enseñan en 6.° y Uruguay en 5.°. Abre la unidad antes del multímetro. Se paga con la fusión 9.</t>
         </is>
       </c>
     </row>
@@ -957,46 +951,46 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>G06-CIE-U1-1.4, G06-CIE-U1-1.5</t>
+          <t>G08-CIE-U1-1.12, G08-CIE-U1-1.13</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1. Fluidos. (después de 4.7 y 4.8, o con referencia a ellos)</t>
+          <t>1. Mecánica</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1.4. Demostración experimental de la capilaridad y la tensión superficial y su explicación por la atracción entre partículas.</t>
+          <t>1.12. Indagación experimental del cambio del momento lineal a partir de la fuerza y el tiempo de interacción.</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Observa el ascenso del agua en tubos o en papel y la flotación de un clip en el agua, y explica ambos fenómenos con la atracción entre partículas.</t>
+          <t>Mide en un experimento cómo cambia el momento lineal de un objeto al variar la fuerza y el tiempo de contacto, y relaciona ese cambio con el impulso.</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Tensión superficial y capilaridad, Fuerzas intermoleculares</t>
+          <t>Momento lineal e impulso</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>fusión: ambos temas trabajan Tensión superficial y capilaridad (4.7 y 4.8 también); prerrequisito: Fuerzas intermoleculares (hoy en 10.°) de Tensión superficial y capilaridad (6.°), confianza alta</t>
+          <t>fusión: ambos temas trabajan Momento lineal e impulso</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Vinculación y demostración de la capilaridad son el mismo contenido. El tema unido introduce la atracción entre partículas que hoy falta como prerrequisito. Libera el tema de la acción 8.</t>
+          <t>Indagación y experimentación con el cambio del momento lineal son el mismo contenido en dos temas. Libera el tema de la acción 8.</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1013,32 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>3. Electricidad y magnetismo. (antes de 3.1)</t>
+          <t>2. Calor y temperatura. (después de 2.3)</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>3.10. Demostración experimental de la electrización de los cuerpos por frotamiento, contacto e inducción.</t>
+          <t>2.8. Indagación del equilibrio térmico y del calor como energía que pasa del cuerpo más caliente al más frío.</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Electriza objetos por frotamiento, contacto e inducción, observa atracción y repulsión y lo explica con el paso de electrones entre los cuerpos.</t>
+          <t>Registra la temperatura de agua caliente y fría al ponerlas en contacto hasta que se igualan y explica el resultado como transferencia de energía entre partículas.</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>Carga eléctrica y electrización</t>
+          <t>Equilibrio térmico y ley cero, Calor como energía en tránsito, Calentamiento y enfriamiento</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>CO 6, UY 5 (Carga eléctrica y electrización); prerrequisito: Carga eléctrica y electrización (hoy en 9.°, G09-CIE-U6-6.1) de Corriente, voltaje y resistencia (6.°), confianza alta</t>
+          <t>AU 2, ENG 6, SG 4, UY 5 (Equilibrio térmico y ley cero); ENG 6, SG 4, UY 3 (Calor como energía en tránsito); AU 2, CO 2, ENG 6, SG 4 (Calentamiento y enfriamiento); bloqueos resueltos en 6.°: Temperatura y escalas termométricas (2.2, 2.3); Modelo de partículas de la materia (2.1)</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>En 6.° se mide la corriente sin haber visto la carga eléctrica, que llega en 9.°. Colombia y Uruguay la enseñan en 5.° y 6.°. Abre la unidad antes del multímetro. Se paga con la fusión 11.</t>
+          <t>Calor y equilibrio térmico llegan hoy en 9.° y 10.°. Se introducen en 6.°, después de sus bloqueos (temperatura y modelo de partículas), y antes de propagación y propiedades térmicas. Se paga con la fusión 11.</t>
         </is>
       </c>
     </row>
@@ -1059,7 +1053,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>G08-CIE-U1-1.12, G08-CIE-U1-1.13</t>
+          <t>G08-CIE-U3-3.5, G08-CIE-U3-3.6</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
@@ -1073,32 +1067,32 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1. Mecánica</t>
+          <t>3. Ondas mecánicas</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1.12. Indagación experimental del cambio del momento lineal a partir de la fuerza y el tiempo de interacción.</t>
+          <t>3.5. Diseño de un experimento para calcular una altura con el período de un péndulo simple.</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Mide en un experimento cómo cambia el momento lineal de un objeto al variar la fuerza y el tiempo de contacto, y relaciona ese cambio con el impulso.</t>
+          <t>Diseña y realiza un experimento que usa el período de un péndulo para estimar una altura y compara el resultado con una medición directa.</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Momento lineal e impulso</t>
+          <t>Péndulo simple</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>fusión: ambos temas trabajan Momento lineal e impulso</t>
+          <t>fusión: ambos temas trabajan Péndulo simple (3.1 a 3.4 también)</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>Indagación y experimentación con el cambio del momento lineal son el mismo contenido en dos temas. Libera el tema de la acción 10.</t>
+          <t>El péndulo simple ocupa seis temas en 8.°. Calcular una altura con el péndulo y diseñar el experimento para hacerlo son el mismo contenido. Libera el tema de la acción 10.</t>
         </is>
       </c>
     </row>
@@ -1108,45 +1102,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>nuevo</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr"/>
+          <t>mover</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>G08-CIE-U1-1.6, G08-CIE-U2-2.1, G08-CIE-U2-2.3, G08-CIE-U2-2.2, G08-CIE-U2-2.7, G08-CIE-U2-2.8</t>
+        </is>
+      </c>
       <c r="D13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="3" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="F13" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2. Calor y temperatura. (después de 2.3)</t>
+          <t>7. Trabajo y energía (después de 6. Ambiente y energía)</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>2.8. Indagación del equilibrio térmico y del calor como energía que pasa del cuerpo más caliente al más frío.</t>
+          <t>7.1. Aplicación del diagrama de cuerpo libre a partir de la identificación experimental de las fuerzas que actúan sobre un objeto, incluida la fricción. | 7.2. Indagación del concepto de trabajo utilizando máquinas simples. | 7.3. Interpretación de los signos del trabajo a partir de la experimentación. | 7.4. Resolución de problemas empleando el teorema del trabajo y la energía cinética. | 7.6. Experimentación con la ley de conservación de la energía mecánica. | 7.7. Interpretación de las gráficas de energía cinética y potencial obtenidas a partir de un experimento.</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>Registra la temperatura de agua caliente y fría al ponerlas en contacto hasta que se igualan y explica el resultado como transferencia de energía entre partículas.</t>
+          <t>Dibuja el diagrama de cuerpo libre de un objeto e identifica peso, normal, tensión y fricción. | Calcula el trabajo realizado con una palanca o una polea y lo compara con el realizado sin ella. | Explica con ejemplos medidos cuándo una fuerza realiza trabajo positivo, negativo o nulo. | Calcula la rapidez final de un objeto a partir del trabajo neto realizado sobre él. | Comprueba en un plano inclinado o un riel que la suma de energía cinética y potencial se mantiene si la fricción es pequeña. | Construye e interpreta gráficas de energía cinética, potencial y total a partir de datos propios.</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>Equilibrio térmico y ley cero, Calor como energía en tránsito, Calentamiento y enfriamiento</t>
+          <t>Fuerza neta y diagrama de cuerpo libre, Fuerzas mecánicas comunes, Fricción y resistencia del aire, Trabajo mecánico, Máquinas simples, Energía cinética, Conservación de la energía mecánica</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>SG 4, UY 5 (Equilibrio térmico y ley cero); SG 4, UY 3 (Calor como energía en tránsito); CO 2, SG 4 (Calentamiento y enfriamiento); bloqueos resueltos en 6.°: Temperatura y escalas termométricas (2.2, 2.3); Modelo de partículas de la materia (2.1)</t>
+          <t>AU 8, CO 8.5, ENG 6, UY 6 (Conservación de la energía): su bloqueo, Conservación de la energía mecánica, debe llegar a 7.°; AU 6, CO 4.5, ENG 6 (Fuerza neta y diagrama de cuerpo libre); ENG 6, SG 6 (Fuerzas mecánicas comunes); ENG 6, UY 5 (Trabajo mecánico); prerrequisito: Fuerzas mecánicas comunes de Trabajo mecánico (1.6 viaja con el trabajo); prerrequisito: Fricción y resistencia del aire (hoy en 10.°) de Fuerzas mecánicas comunes, confianza alta</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>Calor y equilibrio térmico llegan hoy en 9.° y 10.°. Se introducen en 6.°, después de sus bloqueos (temperatura y modelo de partículas), y antes de propagación y propiedades térmicas. Se paga con la fusión 13.</t>
+          <t>Inglaterra, Australia y Singapur enseñan fuerzas, diagrama de cuerpo libre y trabajo en 6.°. Pasan a 7.°, no a 6.°, para dar a 7.° el 15 % del ciclo; 6.° ya recibe dos temas nuevos. Rotación, péndulo y momento siguen en 8.°.</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>G08-CIE-U3-3.5, G08-CIE-U3-3.6</t>
+          <t>G08-CIE-U2-2.9, G08-CIE-U2-2.11</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
@@ -1171,36 +1171,36 @@
         <v>8</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>3. Ondas mecánicas</t>
+          <t>7. Trabajo y energía (después de 7.4)</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3.5. Diseño de un experimento para calcular una altura con el período de un péndulo simple.</t>
+          <t>7.5. Indagación del concepto de potencia mecánica y resolución de problemas.</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Diseña y realiza un experimento que usa el período de un péndulo para estimar una altura y compara el resultado con una medición directa.</t>
+          <t>Mide su propia potencia al subir escaleras y resuelve problemas que relacionan trabajo, tiempo y potencia.</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>Péndulo simple</t>
+          <t>Potencia mecánica</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>fusión: ambos temas trabajan Péndulo simple (3.1 a 3.4 también)</t>
+          <t>fusión: ambos temas trabajan Potencia mecánica (2.10 también); prerrequisito: Trabajo mecánico (acción 12)</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>El péndulo simple ocupa seis temas en 8.°. Calcular una altura con el péndulo y diseñar el experimento para hacerlo son el mismo contenido. Libera el tema de la acción 12.</t>
+          <t>Concepto y problemas de potencia se unen y pasan a 7.° con el trabajo, su prerrequisito. El cálculo con momento lineal (2.10) queda en 8.°. Libera el tema de la acción 14.</t>
         </is>
       </c>
     </row>
@@ -1210,51 +1210,45 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>mover</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>G08-CIE-U1-1.6, G08-CIE-U2-2.1, G08-CIE-U2-2.3, G08-CIE-U2-2.2, G08-CIE-U2-2.7, G08-CIE-U2-2.8</t>
-        </is>
-      </c>
+          <t>nuevo</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr"/>
       <c r="D15" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E15" s="3" t="n"/>
       <c r="F15" s="3" t="n">
         <v>7</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>7. Trabajo y energía (después de 6. Ambiente y energía)</t>
+          <t>7. Trabajo y energía (después de 7.7)</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>7.1. Aplicación del diagrama de cuerpo libre a partir de la identificación experimental de las fuerzas que actúan sobre un objeto, incluida la fricción. | 7.2. Indagación del concepto de trabajo utilizando máquinas simples. | 7.3. Interpretación de los signos del trabajo a partir de la experimentación. | 7.4. Resolución de problemas empleando el teorema del trabajo y la energía cinética. | 7.6. Experimentación con la ley de conservación de la energía mecánica. | 7.7. Interpretación de las gráficas de energía cinética y potencial obtenidas a partir de un experimento.</t>
+          <t>7.8. Análisis de la conservación de la energía y de su disipación en máquinas y dispositivos, con cálculo de su eficiencia.</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>Dibuja el diagrama de cuerpo libre de un objeto e identifica peso, normal, tensión y fricción. | Calcula el trabajo realizado con una palanca o una polea y lo compara con el realizado sin ella. | Explica con ejemplos medidos cuándo una fuerza realiza trabajo positivo, negativo o nulo. | Calcula la rapidez final de un objeto a partir del trabajo neto realizado sobre él. | Comprueba en un plano inclinado o un riel que la suma de energía cinética y potencial se mantiene si la fricción es pequeña. | Construye e interpreta gráficas de energía cinética, potencial y total a partir de datos propios.</t>
+          <t>Representa en un diagrama de flujo de energía un aparato cotidiano, identifica la energía disipada como calor y calcula su eficiencia.</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>Fuerza neta y diagrama de cuerpo libre, Fuerzas mecánicas comunes, Fricción y resistencia del aire, Trabajo mecánico, Máquinas simples, Energía cinética, Conservación de la energía mecánica</t>
+          <t>Conservación de la energía, Disipación de energía y eficiencia, Transformaciones de la energía</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>CO 8, UY 6 (Conservación de la energía): su bloqueo, Conservación de la energía mecánica, debe llegar a 7.°; prerrequisito: Fuerzas mecánicas comunes de Trabajo mecánico (1.6 viaja con el trabajo); prerrequisito: Fricción y resistencia del aire (hoy en 10.°) de Fuerzas mecánicas comunes, confianza alta; prerrequisito: Fuerza neta y diagrama de cuerpo libre (8.°) de Primera ley de Newton (5.°), brecha 3 → 2</t>
+          <t>AU 8, CO 8.5, ENG 6, UY 6 (Conservación de la energía); AU 8, CO 7, UY 6 (Disipación de energía y eficiencia); bloqueo resuelto: Conservación de la energía mecánica (7.6, acción 12)</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>7.° tiene hoy dos temas de Física y 8.°, 37. Pasan a 7.° el trabajo y la conservación de la energía mecánica, con el diagrama de cuerpo libre (incluida la fricción), que el trabajo necesita. Los temas de rotación, péndulo y momento siguen en 8.°.</t>
+          <t>Conservación de la energía y eficiencia llegan hoy en 10.°. Los países las enseñan entre 6.° y 8.° (Australia en 8.°). Cierra la unidad de 7.° y conecta con 6.5 y 6.6 (combustibles y electricidad).</t>
         </is>
       </c>
     </row>
@@ -1264,51 +1258,51 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>fusionar</t>
+          <t>revisar</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>G08-CIE-U2-2.9, G08-CIE-U2-2.11</t>
+          <t>G06-CIE-U3-3.2</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>7. Trabajo y energía (después de 7.4)</t>
+          <t>3. Electricidad y magnetismo.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7.5. Indagación del concepto de potencia mecánica y resolución de problemas.</t>
+          <t>3.2. Identificación del valor de resistencias eléctricas y comprobación experimental de la relación entre voltaje y corriente (ley de Ohm).</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Mide su propia potencia al subir escaleras y resuelve problemas que relacionan trabajo, tiempo y potencia.</t>
+          <t>Mide voltaje y corriente en una resistencia, grafica los datos y reconoce que su cociente es constante e igual al valor de la resistencia.</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>Potencia mecánica</t>
+          <t>Corriente, voltaje y resistencia, Ley de Ohm</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>fusión: ambos temas trabajan Potencia mecánica (2.10 también); prerrequisito: Trabajo mecánico (acción 14)</t>
+          <t>prerrequisito: Ley de Ohm (hoy en 11.°) de Resistencia equivalente (6.°), confianza alta</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>Concepto y problemas de potencia se unen y pasan a 7.° con el trabajo, su prerrequisito. El cálculo con momento lineal (2.10) queda en 8.°. Libera el tema de la acción 16.</t>
+          <t>Corrige sin gastar presupuesto una secuencia invertida de 5 grados: los temas 3.5 y 3.7 calculan resistencias equivalentes sin la ley de Ohm, que el tema 3.2 ya puede introducir.</t>
         </is>
       </c>
     </row>
@@ -1318,45 +1312,51 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>nuevo</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr"/>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>G05-CIE-U2-2.8</t>
+        </is>
+      </c>
       <c r="D17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="3" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="F17" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>7. Trabajo y energía (después de 7.7)</t>
+          <t>2. Mecánica.</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>7.8. Análisis de la conservación de la energía y de su disipación en máquinas y dispositivos, con cálculo de su eficiencia.</t>
+          <t>2.8. Experimentación con el principio de inercia y con la suma de las fuerzas que actúan sobre un objeto, incluida la fricción.</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>Representa en un diagrama de flujo de energía un aparato cotidiano, identifica la energía disipada como calor y calcula su eficiencia.</t>
+          <t>Representa con flechas las fuerzas sobre un objeto, incluida la fricción, reconoce cuándo se equilibran y explica que sin fuerza neta el objeto sigue en reposo o en movimiento uniforme.</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>Conservación de la energía, Disipación de energía y eficiencia, Transformaciones de la energía</t>
+          <t>Primera ley de Newton: inercia, Fricción y resistencia del aire</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>CO 8, UY 6 (Conservación de la energía); CO 7, UY 6 (Disipación de energía y eficiencia); bloqueo resuelto: Conservación de la energía mecánica (7.6, acción 14)</t>
+          <t>prerrequisito: Fuerza neta y diagrama de cuerpo libre (8.°) de Primera ley de Newton: inercia (5.°), confianza alta; AU 3, ENG 2, SG 6 (Fricción y resistencia del aire; hoy en 10.°, G10-FIS-U5-5.9)</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>La conservación de la energía y la eficiencia llegan hoy en 10.°. Uruguay las enseña en 6.° y Colombia en 7.° y 8.°. Cierra la unidad de 7.° y conecta con 6.5 y 6.6 (combustibles y electricidad).</t>
+          <t>Introduce, sin gastar presupuesto, la fuerza neta con flechas y la fricción, que Inglaterra y Australia enseñan en 2.° y 3.° y El Salvador en 10.°. El diagrama formal llega en 7.° (acción 12).</t>
         </is>
       </c>
     </row>
@@ -1371,46 +1371,46 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>G06-CIE-U3-3.2</t>
+          <t>G08-CIE-U1-1.8</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3. Electricidad y magnetismo.</t>
+          <t>1. Mecánica</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3.2. Identificación del valor de resistencias eléctricas y comprobación experimental de la relación entre voltaje y corriente (ley de Ohm).</t>
+          <t>1.8. Resolución de problemas del movimiento rectilíneo, incluida la caída libre, empleando la interpretación de gráficas.</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Mide voltaje y corriente en una resistencia, grafica los datos y reconoce que su cociente es constante e igual al valor de la resistencia.</t>
+          <t>Interpreta gráficas de posición, velocidad y aceleración de un movimiento rectilíneo y resuelve problemas de caída libre con aceleración constante.</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Corriente, voltaje y resistencia, Ley de Ohm</t>
+          <t>Gráficas del movimiento, Movimiento con aceleración constante, Rapidez y velocidad, Caída libre</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>prerrequisito: Ley de Ohm (hoy en 11.°) de Resistencia equivalente (6.°), confianza alta</t>
+          <t>prerrequisito: Caída libre (hoy en 10.°) de Cinemática en dos dimensiones y proyectiles (8.°), confianza alta</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>Corrige sin gastar presupuesto una secuencia invertida de 5 grados: los temas 3.5 y 3.7 calculan resistencias equivalentes sin la ley de Ohm, que el tema 3.2 ya puede introducir.</t>
+          <t>El movimiento parabólico (1.9) se resuelve en 8.° sin caída libre, que llega en 10.°. Incluirla en 1.8, el tema anterior, corrige la secuencia sin gastar presupuesto.</t>
         </is>
       </c>
     </row>
@@ -1420,51 +1420,51 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>revisar</t>
+          <t>mover</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>G05-CIE-U2-2.8</t>
+          <t>G08-CIE-U3-3.7, G08-CIE-U3-3.10, G08-CIE-U3-3.9, G08-CIE-U3-3.12</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2. Mecánica.</t>
+          <t>8. Ondas, sonido y luz (después de 7. Trabajo y energía)</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>2.8. Experimentación con el principio de inercia y con la suma de fuerzas que actúan sobre un objeto.</t>
+          <t>8.1. Identificación experimental del tipo de onda a partir del movimiento de la fuente de vibración en cuerdas. | 8.2. Identificación experimental del tipo de onda a partir del movimiento de la fuente de vibración en columnas de aire. | 8.3. Interpretación de las gráficas de desplazamiento contra posición y contra tiempo de una onda transversal. | 8.4. Explicación del sonido como onda longitudinal a partir de las gráficas de presión y densidad del aire.</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>Representa con flechas las fuerzas sobre un objeto, reconoce cuándo se equilibran y explica que sin fuerza neta el objeto sigue en reposo o en movimiento uniforme.</t>
+          <t>Distingue con un resorte y una cuerda las ondas transversales de las longitudinales según la dirección de vibración. | Relaciona la vibración de la columna de aire de un tubo con la onda sonora que produce. | Lee en una gráfica la amplitud, la longitud de onda y el período y calcula la rapidez de la onda. | Explica con un esquema de compresiones y enrarecimientos por qué el sonido necesita un medio.</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>Primera ley de Newton: inercia</t>
+          <t>Ondas mecánicas transversales y longitudinales, Longitud de onda, frecuencia y rapidez, El sonido como onda mecánica</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>prerrequisito: Fuerza neta y diagrama de cuerpo libre (8.°) de Primera ley de Newton: inercia (5.°), confianza alta</t>
+          <t>AU 8, ENG 2, UY 6 (El sonido como onda mecánica); prerrequisito: Ondas mecánicas transversales y longitudinales (bloqueo, viaja con 3.7 y 3.10); prerrequisito: Longitud de onda, frecuencia y rapidez de Ondas electromagnéticas y espectro (acción 19)</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>Introduce la idea de fuerza neta con flechas, sin diagrama formal, para que la inercia no se enseñe sin ella. El diagrama de cuerpo libre formal llega en 7.° (acción 14).</t>
+          <t>Los países enseñan el sonido como onda entre 2.° y 8.°. Se suben a 7.° las bases de las ondas, con su bloqueo, para preparar el espectro electromagnético. Péndulo, tono en cuerdas y tubos y ondas estacionarias siguen en 8.°.</t>
         </is>
       </c>
     </row>
@@ -1474,51 +1474,99 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>revisar</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>G08-CIE-U1-1.8</t>
-        </is>
-      </c>
+          <t>nuevo</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr"/>
       <c r="D20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="2" t="n"/>
+      <c r="F20" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>8. Ondas, sonido y luz (después de 8.4)</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>8.5. Explicación de la luz como onda electromagnética y del espectro electromagnético.</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Ordena en un esquema del espectro las ondas de radio, microondas, infrarrojo, luz visible, ultravioleta y rayos X según su longitud de onda, reconoce que todas viajan a la rapidez de la luz y da un uso de cada una.</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Ondas electromagnéticas y espectro, Rapidez de la luz</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>CO 8.5, ENG 6, UY 6 (Ondas electromagnéticas y espectro); prerrequisito: Ondas electromagnéticas y espectro (hoy en 10.°) de Absorción de radiación y efecto invernadero (7.°), confianza alta; T8_27-P3.1 Propiedades de la luz (reforzar: 0 temas); bloqueos: Longitud de onda (acción 18); Rapidez de la luz (11.°), se introduce como dato en el mismo tema</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>Inglaterra y Uruguay enseñan el espectro en 6.°; El Salvador, en 10.°. En 7.° corrige la secuencia del efecto invernadero (7.°) y refuerza el objetivo P3.1. Se paga con la fusión 20.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>fusionar</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>G08-CIE-U2-2.4, G08-CIE-U2-2.5</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="F20" s="2" t="n">
+      <c r="F21" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>1. Mecánica</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>1.8. Resolución de problemas del movimiento rectilíneo, incluida la caída libre, empleando la interpretación de gráficas.</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>Interpreta gráficas de posición, velocidad y aceleración de un movimiento rectilíneo y resuelve problemas de caída libre con aceleración constante.</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>Gráficas del movimiento, Movimiento con aceleración constante, Rapidez y velocidad, Caída libre</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>prerrequisito: Caída libre (hoy en 10.°) de Cinemática en dos dimensiones y proyectiles (8.°), confianza alta</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>El movimiento parabólico (1.9) se resuelve en 8.° sin caída libre, que llega en 10.°. Incluirla en 1.8, el tema anterior, corrige la secuencia sin gastar presupuesto.</t>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>2. Energía</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>2.4. Indagación del trabajo de rotación y del momento de inercia en objetos que rotan.</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>Compara cómo giran objetos con la misma masa y distinta distribución y relaciona el momento de inercia con el trabajo necesario para hacerlos rotar.</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>Dinámica y energía de rotación, Torque o momento de fuerza, Trabajo mecánico</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>fusión: ambos temas trabajan Dinámica y energía de rotación (2.6 también)</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>Trabajo de rotación y momento de inercia ocupan dos temas que se estudian juntos en un mismo experimento. Libera el tema de la acción 19.</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1632,7 @@
         <v>23</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D2" s="4">
         <f>C2-B2</f>
@@ -1604,7 +1652,7 @@
         <v>6</v>
       </c>
       <c r="B3" s="4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C3" s="4" t="n">
         <v>24</v>
@@ -1630,7 +1678,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D4" s="4">
         <f>C4-B4</f>
@@ -1653,7 +1701,7 @@
         <v>37</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D5" s="4">
         <f>C5-B5</f>

--- a/asignaturas/fisica/propuesta/Propuesta_Fisica_G05-G08.xlsx
+++ b/asignaturas/fisica/propuesta/Propuesta_Fisica_G05-G08.xlsx
@@ -562,27 +562,27 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>5.9. Observación experimental de los polos de un imán y de sus líneas de campo magnético.</t>
+          <t>5.9. Observación experimental de los polos de un imán, de los materiales que atrae y de sus líneas de campo magnético.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Identifica los polos de un imán por atracción y repulsión y dibuja las líneas de campo que revelan las limaduras de hierro alrededor de un imán de barra.</t>
+          <t>Identifica los polos de un imán por atracción y repulsión, clasifica objetos en magnéticos y no magnéticos y dibuja las líneas de campo que revelan las limaduras de hierro alrededor de un imán de barra.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Imanes y polos magnéticos, Campo magnético y magnetismo terrestre</t>
+          <t>Imanes y polos magnéticos, Materiales magnéticos, Campo magnético y magnetismo terrestre</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>AU 3, CO 2, ENG 2, SG 3, UY 5 (Imanes y polos magnéticos); prerrequisito: Imanes y polos magnéticos (6.°) de Campo magnético y magnetismo terrestre (5.°), confianza alta</t>
+          <t>AU 3, CO 2, ENG 2, JP 2, SG 3, UY 5 (Imanes y polos magnéticos); ENG 2, JP 2, SG 3 (Materiales magnéticos; bloqueo Imanes y polos magnéticos resuelto en el mismo tema); prerrequisito: Imanes y polos magnéticos (6.°) de Campo magnético y magnetismo terrestre (5.°), confianza alta</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>Hoy el campo magnético terrestre (5.9) se estudia un año antes que los imanes. Los cinco países, incluidos Inglaterra, Australia y Singapur, enseñan los imanes entre 2.° y 5.°. El tema pasa a 5.°, antes de 5.9.</t>
+          <t>Hoy el campo magnético terrestre (5.9) se estudia un año antes que los imanes. Los seis países, con Japón, enseñan los imanes entre 2.° y 5.°; Japón, Inglaterra y Singapur, también qué materiales atraen. Pasa a 5.°, antes de 5.9.</t>
         </is>
       </c>
     </row>
@@ -610,27 +610,27 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>10.1. Clasificación experimental de materiales como conductores o aislantes eléctricos.</t>
+          <t>10.1. Construcción de un circuito eléctrico simple y clasificación experimental de materiales como conductores o aislantes.</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>Arma un circuito de prueba con pila y bombillo, comprueba con él distintos materiales y los clasifica en una tabla como conductores o aislantes.</t>
+          <t>Arma un circuito con pila, cables y bombillo, explica por qué el bombillo enciende solo si el circuito está cerrado y lo usa para clasificar en una tabla distintos materiales como conductores o aislantes.</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>Conductores y aislantes eléctricos</t>
+          <t>Circuito eléctrico simple, Conductores y aislantes eléctricos</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>AU 5, CO 4.5, ENG 2, SG 5 (Conductores y aislantes eléctricos); prerrequisito: Conductores y aislantes eléctricos (hoy en 11.°, G11-FIS-U6-6.3) de Circuito eléctrico simple (6.°), confianza alta</t>
+          <t>AU 5, CO 4.5, ENG 2, JP 2, SG 5 (Conductores y aislantes eléctricos); AU 5, CO 2, ENG 2, JP 2, SG 5, UY 5 (Circuito eléctrico simple; bloqueo Conductores y aislantes resuelto en el mismo tema); prerrequisito: Conductores y aislantes eléctricos (hoy en 11.°, G11-FIS-U6-6.3) de Circuito eléctrico simple (6.°), confianza alta</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>Hoy llega en 11.°, cinco grados después de los circuitos de 6.°. Inglaterra, Australia, Singapur y Colombia lo enseñan entre 2.° y 5.°. Se paga con la fusión 3.</t>
+          <t>Los conductores llegan hoy en 11.°, cinco grados después de los circuitos de 6.°. Los cuatro países de alto desempeño enseñan circuito simple y conductores entre 2.° y 5.°. Se paga con la fusión 3.</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2. Mecánica. (después de 2.9)</t>
+          <t>10. Electricidad y luz</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>2.16. Explicación de la gravedad como atracción entre masas y del peso como la fuerza con que la Tierra atrae los objetos.</t>
+          <t>10.2. Experimentación con la reflexión de la luz y la formación de imágenes en espejos planos.</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Explica con ejemplos (caída de objetos, órbita de la Luna) que todos los cuerpos con masa se atraen y distingue masa y peso con un dinamómetro.</t>
+          <t>Usa una linterna y un espejo plano para comprobar que el ángulo de incidencia es igual al de reflexión y describe la imagen que forma el espejo (tamaño, distancia, inversión lateral).</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>Ley de gravitación universal, Gravedad: atracción hacia la Tierra, Masa y peso</t>
+          <t>Reflexión de la luz, Espejos planos e imágenes</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>CO 4.5, ENG 6, UY 5 (Ley de gravitación universal); hoy solo en 10.° (G10-FIS-U5-5.7)</t>
+          <t>AU 4, CO 3, ENG 2, JP 2, SG 4, UY 4 (Reflexión de la luz); T8_27-P3.1 Propiedades de la luz (reforzar: 0 temas en el ciclo); ENG 6, UY 4 (Espejos planos e imágenes; bloqueo Reflexión de la luz resuelto en el mismo tema)</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>Colombia y Uruguay introducen la gravitación en 4.° y 5.° e Inglaterra en 6.°; El Salvador, en 10.°. Se trata de forma cualitativa; el cálculo sigue en 10.°. Se paga con la fusión 5.</t>
+          <t>La luz no aparece en ningún tema de 5.° a 8.° y el objetivo TIMSS P3.1 queda sin cobertura. Los seis países, con Japón en 2.°, enseñan la reflexión entre 2.° y 4.°. Se paga con la fusión 5.</t>
         </is>
       </c>
     </row>
@@ -747,46 +747,46 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>G05-CIE-U1-1.1, G05-CIE-U1-1.2</t>
+          <t>G06-CIE-U1-1.4, G06-CIE-U1-1.5</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1. Magnitudes físicas.</t>
+          <t>1. Fluidos. (coordinar con Química: 4.7 y 4.8 de 6.°, fuerzas intermoleculares)</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1.1. Medición directa de magnitudes físicas en unidades fundamentales y derivadas del SI.</t>
+          <t>1.4. Demostración experimental de la capilaridad y la tensión superficial y su explicación por la atracción entre partículas.</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Mide longitudes, masas, tiempos, áreas y volúmenes con el instrumento adecuado y expresa cada resultado con su unidad del SI.</t>
+          <t>Observa el ascenso del agua en tubos o en papel y la flotación de un clip en el agua, y explica ambos fenómenos con la atracción entre partículas.</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Medición de magnitudes con instrumentos, Sistema Internacional de Unidades</t>
+          <t>Tensión superficial y capilaridad, Fuerzas intermoleculares</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>fusión: ambos temas trabajan Medición de magnitudes con instrumentos y Sistema Internacional de Unidades</t>
+          <t>fusión: ambos temas trabajan Tensión superficial y capilaridad</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Medir en unidades fundamentales y en derivadas es la misma práctica con instrumentos distintos. El SI se mantiene en 1.3, 1.4 y 1.6. Libera el tema de la acción 4.</t>
+          <t>Vinculación y demostración de la capilaridad son el mismo contenido. El tema unido explica el fenómeno por la atracción entre partículas, que Química trabaja en 4.7 y 4.8 de 6.°. Libera el tema de la acción 4.</t>
         </is>
       </c>
     </row>
@@ -805,36 +805,36 @@
       </c>
       <c r="E7" s="3" t="n"/>
       <c r="F7" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>10. Electricidad y luz</t>
+          <t>3. Electricidad y magnetismo. (antes de 3.1)</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>10.2. Experimentación con la reflexión de la luz y la formación de imágenes en espejos planos.</t>
+          <t>3.10. Demostración experimental de la electrización de los cuerpos por frotamiento, contacto e inducción.</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Usa una linterna y un espejo plano para comprobar que el ángulo de incidencia es igual al de reflexión y describe la imagen que forma el espejo (tamaño, distancia, inversión lateral).</t>
+          <t>Electriza objetos por frotamiento, contacto e inducción, observa atracción y repulsión y lo explica con el paso de electrones entre los cuerpos.</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>Reflexión de la luz, Espejos planos e imágenes</t>
+          <t>Carga eléctrica y electrización</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>AU 4, CO 3, ENG 2, SG 4, UY 4 (Reflexión de la luz); T8_27-P3.1 Propiedades de la luz (reforzar: 0 temas en el ciclo); ENG 6, UY 4 (Espejos planos e imágenes; bloqueo Reflexión de la luz resuelto en el mismo tema)</t>
+          <t>CO 6, ENG 6, JP 7, UY 5 (Carga eléctrica y electrización); prerrequisito: Carga eléctrica y electrización (hoy en 9.°, G09-CIE-U6-6.1) de Corriente, voltaje y resistencia (6.°), confianza alta</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>La luz no aparece en ningún tema de 5.° a 8.° y el objetivo TIMSS P3.1 queda sin cobertura. Los cinco países enseñan la reflexión entre 2.° y 4.°. Se paga con la fusión 7.</t>
+          <t>En 6.° se mide la corriente sin haber visto la carga eléctrica, que llega en 9.°. Inglaterra la enseña en 6.° y Japón en 7.°. Abre la unidad antes del multímetro. Se paga con la fusión 7.</t>
         </is>
       </c>
     </row>
@@ -849,46 +849,46 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>G06-CIE-U1-1.4, G06-CIE-U1-1.5</t>
+          <t>G08-CIE-U1-1.12, G08-CIE-U1-1.13</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1. Fluidos. (coordinar con Química: 4.7 y 4.8 de 6.°, fuerzas intermoleculares)</t>
+          <t>1. Mecánica</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1.4. Demostración experimental de la capilaridad y la tensión superficial y su explicación por la atracción entre partículas.</t>
+          <t>1.12. Indagación experimental del cambio del momento lineal a partir de la fuerza y el tiempo de interacción.</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Observa el ascenso del agua en tubos o en papel y la flotación de un clip en el agua, y explica ambos fenómenos con la atracción entre partículas.</t>
+          <t>Mide en un experimento cómo cambia el momento lineal de un objeto al variar la fuerza y el tiempo de contacto, y relaciona ese cambio con el impulso.</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Tensión superficial y capilaridad, Fuerzas intermoleculares</t>
+          <t>Momento lineal e impulso</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>fusión: ambos temas trabajan Tensión superficial y capilaridad</t>
+          <t>fusión: ambos temas trabajan Momento lineal e impulso</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Vinculación y demostración de la capilaridad son el mismo contenido. El tema unido explica el fenómeno por la atracción entre partículas, que Química trabaja en 4.7 y 4.8 de 6.°. Libera el tema de la acción 6.</t>
+          <t>Indagación y experimentación con el cambio del momento lineal son el mismo contenido en dos temas. Libera el tema de la acción 6.</t>
         </is>
       </c>
     </row>
@@ -911,32 +911,32 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>3. Electricidad y magnetismo. (antes de 3.1)</t>
+          <t>2. Calor y temperatura. (después de 2.3)</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>3.10. Demostración experimental de la electrización de los cuerpos por frotamiento, contacto e inducción.</t>
+          <t>2.8. Indagación del equilibrio térmico y del calor como energía que pasa del cuerpo más caliente al más frío.</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Electriza objetos por frotamiento, contacto e inducción, observa atracción y repulsión y lo explica con el paso de electrones entre los cuerpos.</t>
+          <t>Registra la temperatura de agua caliente y fría al ponerlas en contacto hasta que se igualan y explica el resultado como transferencia de energía entre partículas.</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>Carga eléctrica y electrización</t>
+          <t>Equilibrio térmico y ley cero, Calor como energía en tránsito</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>CO 6, ENG 6, UY 5 (Carga eléctrica y electrización); prerrequisito: Carga eléctrica y electrización (hoy en 9.°, G09-CIE-U6-6.1) de Corriente, voltaje y resistencia (6.°), confianza alta</t>
+          <t>AU 2, ENG 6, SG 4, UY 5 (Equilibrio térmico y ley cero); ENG 6, SG 4, UY 3 (Calor como energía en tránsito); bloqueos resueltos en 6.°: Temperatura y escalas termométricas (2.2, 2.3); Modelo de partículas de la materia (2.1); Equilibrio térmico, en el mismo tema</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>En 6.° se mide la corriente sin haber visto la carga eléctrica, que llega en 9.°. Inglaterra y Colombia la enseñan en 6.° y Uruguay en 5.°. Abre la unidad antes del multímetro. Se paga con la fusión 9.</t>
+          <t>Calor y equilibrio térmico llegan hoy en 9.° y 10.°; Australia, Singapur e Inglaterra los enseñan entre 2.° y 6.°. Van en 6.°, después de temperatura y modelo de partículas. Se paga con la fusión 9.</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>G08-CIE-U1-1.12, G08-CIE-U1-1.13</t>
+          <t>G08-CIE-U3-3.5, G08-CIE-U3-3.6</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
@@ -965,32 +965,32 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1. Mecánica</t>
+          <t>3. Ondas mecánicas</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1.12. Indagación experimental del cambio del momento lineal a partir de la fuerza y el tiempo de interacción.</t>
+          <t>3.5. Diseño de un experimento para calcular una altura con el período de un péndulo simple.</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Mide en un experimento cómo cambia el momento lineal de un objeto al variar la fuerza y el tiempo de contacto, y relaciona ese cambio con el impulso.</t>
+          <t>Diseña y realiza un experimento que usa el período de un péndulo para estimar una altura y compara el resultado con una medición directa.</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Momento lineal e impulso</t>
+          <t>Péndulo simple</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>fusión: ambos temas trabajan Momento lineal e impulso</t>
+          <t>fusión: ambos temas trabajan Péndulo simple (3.1 a 3.4 también)</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Indagación y experimentación con el cambio del momento lineal son el mismo contenido en dos temas. Libera el tema de la acción 8.</t>
+          <t>El péndulo simple ocupa seis temas en 8.°. Calcular una altura con el péndulo y diseñar el experimento para hacerlo son el mismo contenido. Libera el tema de la acción 8.</t>
         </is>
       </c>
     </row>
@@ -1000,45 +1000,51 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>nuevo</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr"/>
+          <t>mover</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>G08-CIE-U1-1.6, G08-CIE-U2-2.1, G08-CIE-U2-2.3, G08-CIE-U2-2.2, G08-CIE-U2-2.7, G08-CIE-U2-2.8</t>
+        </is>
+      </c>
       <c r="D11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="3" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="F11" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2. Calor y temperatura. (después de 2.3)</t>
+          <t>7. Trabajo y energía (después de 6. Ambiente y energía)</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>2.8. Indagación del equilibrio térmico y del calor como energía que pasa del cuerpo más caliente al más frío.</t>
+          <t>7.1. Aplicación del diagrama de cuerpo libre a partir de la identificación experimental de las fuerzas que actúan sobre un objeto, incluida la fricción. | 7.2. Indagación del trabajo y de la ventaja mecánica utilizando máquinas simples. | 7.3. Interpretación de los signos del trabajo a partir de la experimentación. | 7.4. Resolución de problemas empleando el teorema del trabajo y la energía cinética. | 7.6. Experimentación con la ley de conservación de la energía mecánica. | 7.7. Interpretación de las gráficas de energía cinética y potencial obtenidas a partir de un experimento.</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Registra la temperatura de agua caliente y fría al ponerlas en contacto hasta que se igualan y explica el resultado como transferencia de energía entre partículas.</t>
+          <t>Dibuja el diagrama de cuerpo libre de un objeto e identifica peso, normal, tensión y fricción. | Calcula el trabajo y la ventaja mecánica de una palanca o una polea y los compara con los de levantar la misma carga sin ella. | Explica con ejemplos medidos cuándo una fuerza realiza trabajo positivo, negativo o nulo. | Calcula la rapidez final de un objeto a partir del trabajo neto realizado sobre él. | Comprueba en un plano inclinado o un riel que la suma de energía cinética y potencial se mantiene si la fricción es pequeña. | Construye e interpreta gráficas de energía cinética, potencial y total a partir de datos propios.</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>Equilibrio térmico y ley cero, Calor como energía en tránsito, Calentamiento y enfriamiento</t>
+          <t>Fuerza neta y diagrama de cuerpo libre, Fuerzas mecánicas comunes, Fricción y resistencia del aire, Trabajo mecánico, Máquinas simples, Ventaja mecánica, Energía cinética, Conservación de la energía mecánica</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>AU 2, ENG 6, SG 4, UY 5 (Equilibrio térmico y ley cero); ENG 6, SG 4, UY 3 (Calor como energía en tránsito); AU 2, CO 2, ENG 6, SG 4 (Calentamiento y enfriamiento); bloqueos resueltos en 6.°: Temperatura y escalas termométricas (2.2, 2.3); Modelo de partículas de la materia (2.1)</t>
+          <t>AU 8, CO 8.5, ENG 6, UY 6 (Conservación de la energía): su bloqueo, Conservación de la energía mecánica, debe llegar a 7.°; AU 6, CO 4.5, ENG 6, JP 6 (Fuerza neta y diagrama de cuerpo libre); ENG 6, SG 6 (Fuerzas mecánicas comunes); ENG 6, JP 8, UY 5 (Trabajo mecánico); CO 4, ENG 3, JP 5 (Ventaja mecánica; hoy en 9.°; bloqueo Torque o momento de fuerza resuelto en 5.°, 2.11); prerrequisito: Fuerzas mecánicas comunes de Trabajo mecánico (1.6 viaja con el trabajo); prerrequisito: Fricción y resistencia del aire (hoy en 10.°) de Fuerzas mecánicas comunes, confianza alta</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>Calor y equilibrio térmico llegan hoy en 9.° y 10.°. Se introducen en 6.°, después de sus bloqueos (temperatura y modelo de partículas), y antes de propagación y propiedades térmicas. Se paga con la fusión 11.</t>
+          <t>Australia, Inglaterra y Japón enseñan el diagrama de cuerpo libre en 6.°; Japón, el trabajo en 8.°. Pasan a 7.° y no a 6.° para equilibrar los grados. La ventaja mecánica (ENG 3, JP 5) se suma a máquinas simples.</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1059,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>G08-CIE-U3-3.5, G08-CIE-U3-3.6</t>
+          <t>G08-CIE-U2-2.9, G08-CIE-U2-2.11</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
@@ -1063,36 +1069,36 @@
         <v>8</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3. Ondas mecánicas</t>
+          <t>7. Trabajo y energía (después de 7.4)</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3.5. Diseño de un experimento para calcular una altura con el período de un péndulo simple.</t>
+          <t>7.5. Indagación del concepto de potencia mecánica y resolución de problemas.</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Diseña y realiza un experimento que usa el período de un péndulo para estimar una altura y compara el resultado con una medición directa.</t>
+          <t>Mide su propia potencia al subir escaleras y resuelve problemas que relacionan trabajo, tiempo y potencia.</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Péndulo simple</t>
+          <t>Potencia mecánica</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>fusión: ambos temas trabajan Péndulo simple (3.1 a 3.4 también)</t>
+          <t>fusión: ambos temas trabajan Potencia mecánica (2.10 también); prerrequisito: Trabajo mecánico (acción 10)</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>El péndulo simple ocupa seis temas en 8.°. Calcular una altura con el péndulo y diseñar el experimento para hacerlo son el mismo contenido. Libera el tema de la acción 10.</t>
+          <t>Concepto y problemas de potencia se unen y pasan a 7.° con el trabajo, su prerrequisito. El cálculo con momento lineal (2.10) queda en 8.°. Libera el tema de la acción 12.</t>
         </is>
       </c>
     </row>
@@ -1102,51 +1108,45 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>mover</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>G08-CIE-U1-1.6, G08-CIE-U2-2.1, G08-CIE-U2-2.3, G08-CIE-U2-2.2, G08-CIE-U2-2.7, G08-CIE-U2-2.8</t>
-        </is>
-      </c>
+          <t>nuevo</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr"/>
       <c r="D13" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E13" s="3" t="n"/>
       <c r="F13" s="3" t="n">
         <v>7</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>7. Trabajo y energía (después de 6. Ambiente y energía)</t>
+          <t>7. Trabajo y energía (después de 7.7)</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>7.1. Aplicación del diagrama de cuerpo libre a partir de la identificación experimental de las fuerzas que actúan sobre un objeto, incluida la fricción. | 7.2. Indagación del concepto de trabajo utilizando máquinas simples. | 7.3. Interpretación de los signos del trabajo a partir de la experimentación. | 7.4. Resolución de problemas empleando el teorema del trabajo y la energía cinética. | 7.6. Experimentación con la ley de conservación de la energía mecánica. | 7.7. Interpretación de las gráficas de energía cinética y potencial obtenidas a partir de un experimento.</t>
+          <t>7.8. Análisis de la conservación de la energía y de su disipación en máquinas y dispositivos, con cálculo de su eficiencia.</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>Dibuja el diagrama de cuerpo libre de un objeto e identifica peso, normal, tensión y fricción. | Calcula el trabajo realizado con una palanca o una polea y lo compara con el realizado sin ella. | Explica con ejemplos medidos cuándo una fuerza realiza trabajo positivo, negativo o nulo. | Calcula la rapidez final de un objeto a partir del trabajo neto realizado sobre él. | Comprueba en un plano inclinado o un riel que la suma de energía cinética y potencial se mantiene si la fricción es pequeña. | Construye e interpreta gráficas de energía cinética, potencial y total a partir de datos propios.</t>
+          <t>Representa en un diagrama de flujo de energía un aparato cotidiano, identifica la energía disipada como calor y calcula su eficiencia.</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>Fuerza neta y diagrama de cuerpo libre, Fuerzas mecánicas comunes, Fricción y resistencia del aire, Trabajo mecánico, Máquinas simples, Energía cinética, Conservación de la energía mecánica</t>
+          <t>Conservación de la energía, Disipación de energía y eficiencia, Transformaciones de la energía</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>AU 8, CO 8.5, ENG 6, UY 6 (Conservación de la energía): su bloqueo, Conservación de la energía mecánica, debe llegar a 7.°; AU 6, CO 4.5, ENG 6 (Fuerza neta y diagrama de cuerpo libre); ENG 6, SG 6 (Fuerzas mecánicas comunes); ENG 6, UY 5 (Trabajo mecánico); prerrequisito: Fuerzas mecánicas comunes de Trabajo mecánico (1.6 viaja con el trabajo); prerrequisito: Fricción y resistencia del aire (hoy en 10.°) de Fuerzas mecánicas comunes, confianza alta</t>
+          <t>AU 8, CO 8.5, ENG 6, UY 6 (Conservación de la energía); bloqueo resuelto: Conservación de la energía mecánica (7.6, acción 10)</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>Inglaterra, Australia y Singapur enseñan fuerzas, diagrama de cuerpo libre y trabajo en 6.°. Pasan a 7.°, no a 6.°, para dar a 7.° el 15 % del ciclo; 6.° ya recibe dos temas nuevos. Rotación, péndulo y momento siguen en 8.°.</t>
+          <t>La conservación de la energía llega hoy en 10.°; Inglaterra la enseña en 6.° y Australia en 8.°. Cierra la unidad de 7.° con la disipación y la eficiencia y conecta con 6.5 y 6.6.</t>
         </is>
       </c>
     </row>
@@ -1156,16 +1156,16 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>fusionar</t>
+          <t>mover</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>G08-CIE-U2-2.9, G08-CIE-U2-2.11</t>
+          <t>G08-CIE-U3-3.7, G08-CIE-U3-3.10, G08-CIE-U3-3.9, G08-CIE-U3-3.12</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>8</v>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>7. Trabajo y energía (después de 7.4)</t>
+          <t>8. Ondas, sonido y luz (después de 7. Trabajo y energía)</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7.5. Indagación del concepto de potencia mecánica y resolución de problemas.</t>
+          <t>8.1. Identificación experimental del tipo de onda a partir del movimiento de la fuente de vibración en cuerdas. | 8.2. Identificación experimental del tipo de onda a partir del movimiento de la fuente de vibración en columnas de aire. | 8.3. Interpretación de las gráficas de desplazamiento contra posición y contra tiempo de una onda transversal. | 8.4. Explicación del sonido como onda longitudinal a partir de las gráficas de presión y densidad del aire.</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Mide su propia potencia al subir escaleras y resuelve problemas que relacionan trabajo, tiempo y potencia.</t>
+          <t>Distingue con un resorte y una cuerda las ondas transversales de las longitudinales según la dirección de vibración. | Relaciona la vibración de la columna de aire de un tubo con la onda sonora que produce. | Lee en una gráfica la amplitud, la longitud de onda y el período y calcula la rapidez de la onda. | Explica con un esquema de compresiones y enrarecimientos por qué el sonido necesita un medio.</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>Potencia mecánica</t>
+          <t>Ondas mecánicas transversales y longitudinales, Longitud de onda, frecuencia y rapidez, El sonido como onda mecánica</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>fusión: ambos temas trabajan Potencia mecánica (2.10 también); prerrequisito: Trabajo mecánico (acción 12)</t>
+          <t>AU 8, ENG 2, JP 6, UY 6 (El sonido como onda mecánica); prerrequisito: Ondas mecánicas transversales y longitudinales (bloqueo, viaja con 3.7 y 3.10); prerrequisito: Longitud de onda, frecuencia y rapidez de Ondas electromagnéticas y espectro (acción 14)</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>Concepto y problemas de potencia se unen y pasan a 7.° con el trabajo, su prerrequisito. El cálculo con momento lineal (2.10) queda en 8.°. Libera el tema de la acción 14.</t>
+          <t>Inglaterra, Japón y Australia enseñan el sonido como onda entre 2.° y 8.°. Se suben a 7.° las bases de las ondas, con su bloqueo, para preparar el espectro y la refracción. Péndulo, tono y ondas estacionarias siguen en 8.°.</t>
         </is>
       </c>
     </row>
@@ -1223,32 +1223,32 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>7. Trabajo y energía (después de 7.7)</t>
+          <t>8. Ondas, sonido y luz (después de 8.4)</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>7.8. Análisis de la conservación de la energía y de su disipación en máquinas y dispositivos, con cálculo de su eficiencia.</t>
+          <t>8.5. Explicación de la luz como onda electromagnética y del espectro electromagnético.</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>Representa en un diagrama de flujo de energía un aparato cotidiano, identifica la energía disipada como calor y calcula su eficiencia.</t>
+          <t>Ordena en un esquema del espectro las ondas de radio, microondas, infrarrojo, luz visible, ultravioleta y rayos X según su longitud de onda, reconoce que todas viajan a la rapidez de la luz y da un uso de cada una.</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>Conservación de la energía, Disipación de energía y eficiencia, Transformaciones de la energía</t>
+          <t>Ondas electromagnéticas y espectro, Rapidez de la luz</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>AU 8, CO 8.5, ENG 6, UY 6 (Conservación de la energía); AU 8, CO 7, UY 6 (Disipación de energía y eficiencia); bloqueo resuelto: Conservación de la energía mecánica (7.6, acción 12)</t>
+          <t>CO 8.5, ENG 6, UY 6 (Ondas electromagnéticas y espectro); prerrequisito: Ondas electromagnéticas y espectro (hoy en 10.°) de Absorción de radiación y efecto invernadero (7.°), confianza alta; T8_27-P3.1 Propiedades de la luz (reforzar: 0 temas); bloqueos: Longitud de onda (acción 13); Rapidez de la luz (11.°), se introduce como dato en el mismo tema</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>Conservación de la energía y eficiencia llegan hoy en 10.°. Los países las enseñan entre 6.° y 8.° (Australia en 8.°). Cierra la unidad de 7.° y conecta con 6.5 y 6.6 (combustibles y electricidad).</t>
+          <t>Inglaterra y Uruguay enseñan el espectro en 6.°; El Salvador, en 10.°. En 7.° corrige la secuencia del efecto invernadero (7.°), refuerza P3.1 y aporta la rapidez de la luz que necesita la refracción. Se paga con la fusión 15.</t>
         </is>
       </c>
     </row>
@@ -1258,51 +1258,51 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>revisar</t>
+          <t>fusionar</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>G06-CIE-U3-3.2</t>
+          <t>G08-CIE-U2-2.4, G08-CIE-U2-2.5</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3. Electricidad y magnetismo.</t>
+          <t>2. Energía</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3.2. Identificación del valor de resistencias eléctricas y comprobación experimental de la relación entre voltaje y corriente (ley de Ohm).</t>
+          <t>2.4. Indagación del trabajo de rotación y del momento de inercia en objetos que rotan.</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Mide voltaje y corriente en una resistencia, grafica los datos y reconoce que su cociente es constante e igual al valor de la resistencia.</t>
+          <t>Compara cómo giran objetos con la misma masa y distinta distribución y relaciona el momento de inercia con el trabajo necesario para hacerlos rotar.</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>Corriente, voltaje y resistencia, Ley de Ohm</t>
+          <t>Dinámica y energía de rotación, Torque o momento de fuerza, Trabajo mecánico</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>prerrequisito: Ley de Ohm (hoy en 11.°) de Resistencia equivalente (6.°), confianza alta</t>
+          <t>fusión: ambos temas trabajan Dinámica y energía de rotación (2.6 también)</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>Corrige sin gastar presupuesto una secuencia invertida de 5 grados: los temas 3.5 y 3.7 calculan resistencias equivalentes sin la ley de Ohm, que el tema 3.2 ya puede introducir.</t>
+          <t>Trabajo de rotación y momento de inercia ocupan dos temas que se estudian juntos en un mismo experimento. Libera el tema de la acción 14.</t>
         </is>
       </c>
     </row>
@@ -1312,51 +1312,45 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>revisar</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>G05-CIE-U2-2.8</t>
-        </is>
-      </c>
+          <t>nuevo</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr"/>
       <c r="D17" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E17" s="3" t="n"/>
       <c r="F17" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2. Mecánica.</t>
+          <t>8. Ondas, sonido y luz (después de 8.5)</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>2.8. Experimentación con el principio de inercia y con la suma de las fuerzas que actúan sobre un objeto, incluida la fricción.</t>
+          <t>8.6. Experimentación con la refracción de la luz y la formación de imágenes con lentes convergentes.</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>Representa con flechas las fuerzas sobre un objeto, incluida la fricción, reconoce cuándo se equilibran y explica que sin fuerza neta el objeto sigue en reposo o en movimiento uniforme.</t>
+          <t>Observa y dibuja cómo se desvía un haz de luz al pasar del aire al agua o al vidrio, lo explica por el cambio de rapidez de la luz y localiza la imagen que forma una lupa.</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>Primera ley de Newton: inercia, Fricción y resistencia del aire</t>
+          <t>Refracción de la luz, Lentes delgadas e imágenes</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>prerrequisito: Fuerza neta y diagrama de cuerpo libre (8.°) de Primera ley de Newton: inercia (5.°), confianza alta; AU 3, ENG 2, SG 6 (Fricción y resistencia del aire; hoy en 10.°, G10-FIS-U5-5.9)</t>
+          <t>AU 4, ENG 6, JP 6, UY 5 (Refracción de la luz; hoy en 10.°, G10-FIS-U16-16.8); ENG 6, JP 6, UY 5 (Lentes delgadas e imágenes; bloqueo Refracción de la luz resuelto en el mismo tema); bloqueo resuelto: Rapidez de la luz (hoy en 11.°), introducida en 8.5 (acción 14); T8_27-P3.1 Propiedades de la luz (reforzar: 0 temas en el ciclo)</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>Introduce, sin gastar presupuesto, la fuerza neta con flechas y la fricción, que Inglaterra y Australia enseñan en 2.° y 3.° y El Salvador en 10.°. El diagrama formal llega en 7.° (acción 12).</t>
+          <t>Australia, Inglaterra y Japón enseñan la refracción entre 4.° y 6.°; Inglaterra y Japón, las lentes en 6.°. El Salvador, en 10.°. Va tras el espectro, que aporta la rapidez de la luz. Se paga con la fusión 17.</t>
         </is>
       </c>
     </row>
@@ -1366,51 +1360,51 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>revisar</t>
+          <t>fusionar</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>G08-CIE-U1-1.8</t>
+          <t>G05-CIE-U1-1.1, G05-CIE-U1-1.2</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1. Mecánica</t>
+          <t>1. Magnitudes físicas.</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1.8. Resolución de problemas del movimiento rectilíneo, incluida la caída libre, empleando la interpretación de gráficas.</t>
+          <t>1.1. Medición directa de magnitudes físicas en unidades fundamentales y derivadas del SI.</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Interpreta gráficas de posición, velocidad y aceleración de un movimiento rectilíneo y resuelve problemas de caída libre con aceleración constante.</t>
+          <t>Mide longitudes, masas, tiempos, áreas y volúmenes con el instrumento adecuado y expresa cada resultado con su unidad del SI.</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Gráficas del movimiento, Movimiento con aceleración constante, Rapidez y velocidad, Caída libre</t>
+          <t>Medición de magnitudes con instrumentos, Sistema Internacional de Unidades</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>prerrequisito: Caída libre (hoy en 10.°) de Cinemática en dos dimensiones y proyectiles (8.°), confianza alta</t>
+          <t>fusión: ambos temas trabajan Medición de magnitudes con instrumentos y Sistema Internacional de Unidades</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>El movimiento parabólico (1.9) se resuelve en 8.° sin caída libre, que llega en 10.°. Incluirla en 1.8, el tema anterior, corrige la secuencia sin gastar presupuesto.</t>
+          <t>Medir en unidades fundamentales y en derivadas es la misma práctica con instrumentos distintos. El SI se mantiene en 1.3, 1.4 y 1.6. Libera el tema de la acción 16.</t>
         </is>
       </c>
     </row>
@@ -1420,51 +1414,51 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>mover</t>
+          <t>revisar</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>G08-CIE-U3-3.7, G08-CIE-U3-3.10, G08-CIE-U3-3.9, G08-CIE-U3-3.12</t>
+          <t>G06-CIE-U3-3.2</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>8. Ondas, sonido y luz (después de 7. Trabajo y energía)</t>
+          <t>3. Electricidad y magnetismo.</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>8.1. Identificación experimental del tipo de onda a partir del movimiento de la fuente de vibración en cuerdas. | 8.2. Identificación experimental del tipo de onda a partir del movimiento de la fuente de vibración en columnas de aire. | 8.3. Interpretación de las gráficas de desplazamiento contra posición y contra tiempo de una onda transversal. | 8.4. Explicación del sonido como onda longitudinal a partir de las gráficas de presión y densidad del aire.</t>
+          <t>3.2. Identificación del valor de resistencias eléctricas y comprobación experimental de la relación entre voltaje y corriente (ley de Ohm).</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>Distingue con un resorte y una cuerda las ondas transversales de las longitudinales según la dirección de vibración. | Relaciona la vibración de la columna de aire de un tubo con la onda sonora que produce. | Lee en una gráfica la amplitud, la longitud de onda y el período y calcula la rapidez de la onda. | Explica con un esquema de compresiones y enrarecimientos por qué el sonido necesita un medio.</t>
+          <t>Mide voltaje y corriente en una resistencia, grafica los datos y reconoce que su cociente es constante e igual al valor de la resistencia.</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>Ondas mecánicas transversales y longitudinales, Longitud de onda, frecuencia y rapidez, El sonido como onda mecánica</t>
+          <t>Corriente, voltaje y resistencia, Ley de Ohm</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>AU 8, ENG 2, UY 6 (El sonido como onda mecánica); prerrequisito: Ondas mecánicas transversales y longitudinales (bloqueo, viaja con 3.7 y 3.10); prerrequisito: Longitud de onda, frecuencia y rapidez de Ondas electromagnéticas y espectro (acción 19)</t>
+          <t>ENG 6, JP 7 (Ley de Ohm; hoy en 11.°, G11-FIS-U9-9.2); prerrequisito: Ley de Ohm (hoy en 11.°) de Resistencia equivalente (6.°), confianza alta</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>Los países enseñan el sonido como onda entre 2.° y 8.°. Se suben a 7.° las bases de las ondas, con su bloqueo, para preparar el espectro electromagnético. Péndulo, tono en cuerdas y tubos y ondas estacionarias siguen en 8.°.</t>
+          <t>Corrige sin gastar presupuesto una secuencia invertida de 5 grados: 3.5 y 3.7 calculan resistencias equivalentes sin la ley de Ohm. Inglaterra la enseña en 6.° y Japón en 7.°; el tema 3.2 ya puede introducirla.</t>
         </is>
       </c>
     </row>
@@ -1474,45 +1468,51 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>nuevo</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr"/>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>G05-CIE-U2-2.8</t>
+        </is>
+      </c>
       <c r="D20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="F20" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>8. Ondas, sonido y luz (después de 8.4)</t>
+          <t>2. Mecánica.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8.5. Explicación de la luz como onda electromagnética y del espectro electromagnético.</t>
+          <t>2.8. Experimentación con el principio de inercia y con la suma de las fuerzas que actúan sobre un objeto, incluida la fricción.</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Ordena en un esquema del espectro las ondas de radio, microondas, infrarrojo, luz visible, ultravioleta y rayos X según su longitud de onda, reconoce que todas viajan a la rapidez de la luz y da un uso de cada una.</t>
+          <t>Representa con flechas las fuerzas sobre un objeto, incluida la fricción, reconoce cuándo se equilibran y explica que sin fuerza neta el objeto sigue en reposo o en movimiento uniforme.</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>Ondas electromagnéticas y espectro, Rapidez de la luz</t>
+          <t>Primera ley de Newton: inercia, Fricción y resistencia del aire</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>CO 8.5, ENG 6, UY 6 (Ondas electromagnéticas y espectro); prerrequisito: Ondas electromagnéticas y espectro (hoy en 10.°) de Absorción de radiación y efecto invernadero (7.°), confianza alta; T8_27-P3.1 Propiedades de la luz (reforzar: 0 temas); bloqueos: Longitud de onda (acción 18); Rapidez de la luz (11.°), se introduce como dato en el mismo tema</t>
+          <t>prerrequisito: Fuerza neta y diagrama de cuerpo libre (8.°) de Primera ley de Newton: inercia (5.°), confianza alta; AU 3, ENG 2, SG 6 (Fricción y resistencia del aire; hoy en 10.°, G10-FIS-U5-5.9)</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>Inglaterra y Uruguay enseñan el espectro en 6.°; El Salvador, en 10.°. En 7.° corrige la secuencia del efecto invernadero (7.°) y refuerza el objetivo P3.1. Se paga con la fusión 20.</t>
+          <t>Introduce, sin gastar presupuesto, la fuerza neta con flechas y la fricción, que Inglaterra y Australia enseñan en 2.° y 3.° y El Salvador en 10.°. El diagrama formal llega en 7.° (acción 10).</t>
         </is>
       </c>
     </row>
@@ -1522,16 +1522,16 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>fusionar</t>
+          <t>revisar</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>G08-CIE-U2-2.4, G08-CIE-U2-2.5</t>
+          <t>G08-CIE-U1-1.8</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>8</v>
@@ -1541,32 +1541,32 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2. Energía</t>
+          <t>1. Mecánica</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>2.4. Indagación del trabajo de rotación y del momento de inercia en objetos que rotan.</t>
+          <t>1.8. Resolución de problemas del movimiento rectilíneo, incluida la caída libre por la atracción gravitatoria de la Tierra, empleando la interpretación de gráficas.</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>Compara cómo giran objetos con la misma masa y distinta distribución y relaciona el momento de inercia con el trabajo necesario para hacerlos rotar.</t>
+          <t>Interpreta gráficas de posición, velocidad y aceleración de un movimiento rectilíneo, explica la caída libre como efecto de la atracción de la Tierra y resuelve problemas con aceleración constante.</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>Dinámica y energía de rotación, Torque o momento de fuerza, Trabajo mecánico</t>
+          <t>Gráficas del movimiento, Movimiento con aceleración constante, Rapidez y velocidad, Caída libre, Gravedad: atracción hacia la Tierra</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>fusión: ambos temas trabajan Dinámica y energía de rotación (2.6 también)</t>
+          <t>prerrequisito: Caída libre (hoy en 10.°) de Cinemática en dos dimensiones y proyectiles (8.°), confianza alta; prerrequisito: Gravedad: atracción hacia la Tierra de Caída libre, resuelto en el mismo tema</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>Trabajo de rotación y momento de inercia ocupan dos temas que se estudian juntos en un mismo experimento. Libera el tema de la acción 19.</t>
+          <t>El movimiento parabólico (1.9) se resuelve en 8.° sin caída libre, que llega en 10.°. Incluirla en 1.8, con la gravedad como su causa, corrige la secuencia sin gastar presupuesto.</t>
         </is>
       </c>
     </row>
@@ -1632,7 +1632,7 @@
         <v>23</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D2" s="4">
         <f>C2-B2</f>
@@ -1678,7 +1678,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4" s="4">
         <f>C4-B4</f>

--- a/asignaturas/fisica/propuesta/Propuesta_Fisica_G05-G08.xlsx
+++ b/asignaturas/fisica/propuesta/Propuesta_Fisica_G05-G08.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1473,11 +1473,11 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>G05-CIE-U2-2.8</t>
+          <t>G05-CIE-U2-2.8, G05-CIE-U2-2.9</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>5</v>
@@ -1492,27 +1492,27 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2.8. Experimentación con el principio de inercia y con la suma de las fuerzas que actúan sobre un objeto, incluida la fricción.</t>
+          <t>2.8. Experimentación con fuerzas equilibradas y desequilibradas y su efecto sobre el reposo y el movimiento de un objeto, incluida la fricción. | 2.9. Experimentación de cómo una fuerza desequilibrada, incluida la fricción, acelera o frena un objeto.</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Representa con flechas las fuerzas sobre un objeto, incluida la fricción, reconoce cuándo se equilibran y explica que sin fuerza neta el objeto sigue en reposo o en movimiento uniforme.</t>
+          <t>Representa con flechas los empujes, tirones y la fricción sobre un objeto, reconoce cuándo se equilibran y predice si el objeto arranca, se frena, cambia de dirección o sigue igual. | Comprueba con un carrito que una fuerza mayor o una masa menor producen un cambio de rapidez más grande y que la fricción lo frena.</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>Primera ley de Newton: inercia, Fricción y resistencia del aire</t>
+          <t>Fuerza como empuje o tirón, Fricción y resistencia del aire</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>prerrequisito: Fuerza neta y diagrama de cuerpo libre (8.°) de Primera ley de Newton: inercia (5.°), confianza alta; AU 3, ENG 2, SG 6 (Fricción y resistencia del aire; hoy en 10.°, G10-FIS-U5-5.9)</t>
+          <t>prerrequisito: Fuerza neta y diagrama de cuerpo libre (7.°, acción 10) de Primera ley de Newton: inercia (hoy etiquetada en 5.°), confianza alta; prerrequisito: Primera ley de Newton: inercia de Segunda ley de Newton (hoy etiquetada en 5.°, 2.9), confianza alta; AU 3, ENG 2, SG 6 (Fricción y resistencia del aire; hoy en 10.°, G10-FIS-U5-5.9)</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>Introduce, sin gastar presupuesto, la fuerza neta con flechas y la fricción, que Inglaterra y Australia enseñan en 2.° y 3.° y El Salvador en 10.°. El diagrama formal llega en 7.° (acción 10).</t>
+          <t>Las leyes de Newton se formulan con la fuerza neta, que llega en 7.°. En 5.° los temas tratan, de forma cualitativa, fuerzas equilibradas y desequilibradas y la fricción (ENG 2, AU 3); las leyes se formalizan en 8.° (1.7).</t>
         </is>
       </c>
     </row>
@@ -1567,6 +1567,60 @@
       <c r="L21" s="3" t="inlineStr">
         <is>
           <t>El movimiento parabólico (1.9) se resuelve en 8.° sin caída libre, que llega en 10.°. Incluirla en 1.8, con la gravedad como su causa, corrige la secuencia sin gastar presupuesto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>G08-CIE-U3-3.8, G08-CIE-U3-3.11</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>3. Ondas mecánicas</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>3.8. Identificación experimental de las magnitudes (longitud, tensión y grosor) que varían la frecuencia o el tono del sonido producido en cuerdas. | 3.11. Identificación experimental de las magnitudes (longitud de la columna, extremo abierto o cerrado) que varían la frecuencia o el tono del sonido producido en tubos de aire.</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Mide cómo cambia el tono de una cuerda al variar su longitud, tensión o grosor y resume en una tabla la relación con la frecuencia. | Mide cómo cambia el tono de un tubo al variar la longitud de la columna de aire y explica que una columna más corta vibra con mayor frecuencia.</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Características del sonido: tono, intensidad y eco, Longitud de onda, frecuencia y rapidez</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>prerrequisito: Superposición e interferencia de ondas (11.°) de Ondas estacionarias y armónicos (8.°, 3.8 y 3.11), confianza alta; los temas miden qué magnitudes cambian el tono; no trabajan nodos, antinodos ni armónicos</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>Los temas 3.8 y 3.11 son experimentales sobre el tono; la etiqueta de ondas estacionarias los adelantaba sin la superposición (11.°). Se precisa el alcance sin gastar presupuesto; nodos y armónicos quedan para 11.°.</t>
         </is>
       </c>
     </row>
